--- a/app/spec/SPEC_RFQ_MM_CONSOLE.xlsx
+++ b/app/spec/SPEC_RFQ_MM_CONSOLE.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The maker's curve IS the quote: four Burr-2 parameters (S-bar, a, gamma, kappa) price ANY strike on demand from a closed form; a half-spread h around it makes bid/ask; makers differ in depth (lambda) and spread (h) but share the LEVEL (no smile - proved obstruction); the tradeable book is the envelope; RFQ fills walk makers cheapest-first, each paid at its own posted spread.</t>
+          <t>The maker's curve IS the quote: four Burr-2 parameters (S-bar, a, gamma, kappa) price ANY strike on demand from a closed form; a half-spread h around it makes bid/ask; makers differ in depth (lambda) and spread (h) but share the LEVEL (no smile - a design CHOICE motivated by the proved single-lens obstruction, not forced by it on Burr-2; see sheets 3/8); the tradeable book is the envelope; RFQ fills walk makers cheapest-first, each paid at its own posted spread.</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Single-file index.html (Burr-2 math in JS incl. incomplete beta via continued fraction) + node server + railway.json. Panels: quote params, market, curve vs aggregate book, RFQ ladder, makers, P&amp;L, risk. Parity exact headless. Historical headline: vol-indexed vs fixed-spread APR contrast (build-5-era calibration).</t>
+          <t>Single-file index.html (Burr-2 math in JS incl. incomplete beta via continued fraction) + node server + railway.json. Panels: quote params, market, curve vs aggregate book, RFQ ladder, makers, P&amp;L, risk. Parity exact headless. THIS commit carries the historical vol-indexed vs fixed-spread APR headline (+3.1/+27.7/+110.8 vs +24.5/-74.0/-406.4) - BUILD-1, PRE-basis-fix calibration (sheet 5).</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Operator: tabs were delinked; Transact should show the aggregate curve. Three vantage points on ONE book. REAL BUG found+fixed: per-maker curve params CROSSED the book (bid &gt; ask by 1,261 bps) - makers now share the LEVEL (common curve, no smile) and differ only in depth+spread ("transport-not-level"); honest CROSSED-arb detector added. Result: 16.4 bps best-maker half-spread, clean.</t>
+          <t>Operator: tabs were delinked; Transact should show the aggregate curve. Three vantage points on ONE book. REAL BUG found+fixed: per-maker curve params CROSSED the book (bid &gt; ask; -1,261 bps in HALF-spread convention = -2,522 bps full-spread; NB sheet 5's 32.8 bps is full-spread) - a LEVEL-DISAGREEMENT failure. Fix: makers share the LEVEL and differ only in depth+spread ("transport-not-level"); honest CROSSED-arb detector added. Result: 16.4 bps best-maker half-spread, clean.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>The whole economics layer (bleed, h_fair, APR, viability) is a MODEL with demo constants, no Lean, and the fixed-mode inversion is unreachable at the default fee=0.02 (sheet 5 finding).</t>
+          <t>The whole economics layer (bleed, h_fair, APR, viability) is a MODEL with demo constants, no Lean, and the fixed-mode inversion is unreachable at the default fee=0.02 within the RV slider (needs fee &lt; 1.62%; sheet 5 finding).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -974,49 +974,66 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E-2</t>
+          <t>F-1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Realtime LP tuning (entry 541) converts a passive-LP product into an active-MM venue; LP-vs-LP adverse selection, correlated withdrawal, herding are new risks with no model.</t>
+          <t>SKEPTIC FINDING 2026-08-18 (reported, not fixed): Portfolio "residual exposure 0.000000" is a hardcoded string (index.html L554) over the definitional identity hedge := -netDelta - closure by construction, not a check; a wrong Delta still reads back to zero. And the demo put-leg delta IS wrong: code uses -Delta_call = 0.5358 at k=-0.10, while parity P=C+k forces 0.4642 long (-0.4642 for the short put position).</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>operator-tier, open problem</t>
+          <t>app bug + display honesty, open</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P-1</t>
+          <t>E-2</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>The app is NOT wired to the production engine; nothing here changes engine/ or its gates.</t>
+          <t>Realtime LP tuning (entry 541) converts a passive-LP product into an active-MM venue; LP-vs-LP adverse selection, correlated withdrawal, herding are new risks with no model.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>known</t>
+          <t>operator-tier, open problem</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
+          <t>P-1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>The app is NOT wired to the production engine; nothing here changes engine/ or its gates.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>known</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>T-1</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>The 2026-08-14 app-build session's operator messages were never transcribed (corrigendum filed 2026-08-18); build-history operator quotes are commit-message fragments, labelled reconstruction.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>process, owned by manager</t>
         </is>
@@ -1690,7 +1707,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>THE SETTLED ARCHITECTURE ("transport-not-level"). Reason is a proved theorem: mixture_not_single_lens (LOOP_LINK_A) - heterogeneous steepness generates a strict smile no single power law can represent. Build 11 initially violated this (per-maker params) and the book CROSSED (bid 0.15482 &gt; ask 0.12015); fixed to common level.</t>
+          <t>CHOSEN architecture ("transport-not-level") - MOTIVATED, NOT FORCED, by the proved obstruction: mixture_not_single_lens (LOOP_LINK_A) is proved for the POWER-LAW LENS family; on Burr-2 the corpus's own BURR2_MIXTURE result says heterogeneity is second-order mild and re-fit is practically viable (entry 529), and the envelope need not be one curve. Ratification provenance is RECONSTRUCTION-GRADE (the 2026-08-14 session is untranscribed; transport-not-level enters the transcript as a manager recommendation, entry 513). Build 11's crossed book (bid 0.15482 &gt; ask 0.12015) was a LEVEL-DISAGREEMENT failure - a DISTINCT failure mode from the smile obstruction, not an instance of it; what IS provable: common level + positive spreads cannot cross.</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1843,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>operator rulings entries 514-517 (account-level liquidation, no option funding). Readback has NO Lean (v3-maps G1: Exposure cited in README but absent - still open as of 2026-08-18).</t>
+          <t>operator rulings entries 514-517 (account-level liquidation, no option funding). Readback has NO Lean (v3-maps G1: Exposure cited in README but absent - still open as of 2026-08-18). The displayed "residual exposure 0.000000" is a HARDCODED string atop a definitional identity (hedge := -netDelta), not a computed check; and the demo put-leg delta is not parity-consistent (skeptic finding 2026-08-18, sheet 10 F-1).</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1954,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Demo positions with mark/value/delta; ONE account equity (perps + options), account leverage vs 50x cap with headroom + SAFE/LIQUIDATED status; carve panel (carved notional, equity removed from perps tab); hedge readback: net option delta -&gt; required perp hedge -&gt; residual 0.</t>
+          <t>Demo positions with mark/value/delta; ONE account equity (perps + options), account leverage vs 50x cap with headroom + SAFE/LIQUIDATED status; carve panel (carved notional, equity removed from perps tab); hedge readback: net option delta -&gt; required perp hedge -&gt; "residual 0" (NB the residual-0 line is a hardcoded display of the definitional identity hedge := -netDelta, NOT a computed check - see sheet 10 F-1).</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2463,7 @@
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>FINDING (manager, 2026-08-18): at the shipped default fee=0.02 (=100 bps half-spread) the fixed mode NEVER inverts within the RV slider range [10%,140%] - inversion needs RV &gt; 155% at fee=2%, or fee &lt;= ~1%. The in-app fixed-mode caption ("watch the APR invert") therefore only demonstrates at lower fee settings. The famous build-5 headline (vol-indexed +3.1/+27.7/+110.8% vs fixed +24.5/-74.0/-406.4% APR at RV 20/60/120%) is HISTORICAL - build-5 code and calibration, not reproducible on build-11 defaults.</t>
+          <t>FINDING (manager, 2026-08-18; skeptic re-derived): at the shipped default fee=0.02 (=100 bps half-spread) the fixed mode NEVER inverts within the RV slider range [10%,140%] - inversion needs RV &gt; 155.4% at fee=2%, or fee &lt; 1.62% at the slider max. The in-app fixed-mode caption ("watch the APR invert") therefore only demonstrates at lower fee settings. The headline APR contrast (vol-indexed +3.1/+27.7/+110.8% vs fixed +24.5/-74.0/-406.4% at RV 20/60/120%) is HISTORICAL and belongs to BUILD 1 (commit 75abb52, PRE the build-4 gamma-bleed basis fix) - not reproducible on build-11 defaults. [Corrected from "build-5" per skeptic FLAG F1.]</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>THE LEAN CORPUS — 5 packages, 130 theorems. All: #print axioms = {propext, Classical.choice, Quot.sound}; no sorry/admit/axiom/native_decide/opaque/unsafe; statements byte-identical to submission; locally kernel-verified (Lean 4.28.0, Mathlib oleans from CI cache - stated).</t>
+          <t>THE LEAN CORPUS — 5 packages, 130 theorems. All: #print axioms = {propext, Classical.choice, Quot.sound}; no sorry/admit/axiom/native_decide/opaque/unsafe; statements byte-identical to submission (the 4 Aristotle packages; v3-maps-lean was written in-repo, never submitted); locally kernel-verified (Lean 4.28.0, Mathlib oleans from CI cache - stated).</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2678,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>THEOREM-LEVEL LISTING — the three RFQ-specific packages, all 64 named theorems (v3-maps 54 summarised on sheet 6; full names in its files).</t>
+          <t>THEOREM-LEVEL LISTING — the four RFQ-specific packages, all 76 named theorems (BURR2_CORE 42 + MIXTURE 13 + LINK_A 9 + LINK_B 12; v3-maps 54 summarised on sheet 6, full names in its files).</t>
         </is>
       </c>
     </row>
@@ -3712,17 +3729,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>mixture_not_single_lens (why levels must be shared) + BURR2_MIXTURE (Burr-2 gamma/scale mixtures, second-order bound)</t>
+          <t>mixture_not_single_lens (motivates the shared level) + BURR2_MIXTURE (Burr-2 gamma/scale mixtures, second-order bound)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PROVED</t>
+          <t>PROVED (motivates, does not force)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>the obstruction is proved for the single-power-law lens; the Burr-2 mixture bound is on the MIDPOINT member, near-the-money scope; joint non-closure over all 4 params unproved.</t>
+          <t>the obstruction is proved for the single-POWER-LAW lens family, not for Burr-2, where the mixture effect is second-order and re-fit is practically viable (entry 529) - so common level is a design CHOICE here. Bound caveats: midpoint member, near-the-money scope; joint non-closure over all 4 params unproved. The build-11 crossed book was a level-disagreement failure, distinct from the smile obstruction.</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3871,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>re-verified absent 2026-08-18. The README/loop-map citation must be fixed or the ~10 lines written before this backing is described externally.</t>
+          <t>re-verified absent 2026-08-18. The README/loop-map citation must be fixed or the ~10 lines written before this backing is described externally. ALSO: the UI's "residual exposure 0.000000" is a hardcoded string over the definitional identity hedge := -netDelta (closure-by-construction, same pattern as loop-audit sec 3(i)); a wrong Delta still reads back to zero, and the demo put-leg delta is in fact not parity-consistent (F-1).</t>
         </is>
       </c>
     </row>
